--- a/example_data/connections/connections-input.xlsx
+++ b/example_data/connections/connections-input.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
   <si>
     <t xml:space="preserve">node1</t>
   </si>
@@ -53,91 +53,91 @@
     <t xml:space="preserve">connection_investment_cost</t>
   </si>
   <si>
+    <t xml:space="preserve">efficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ts:price_dayahead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explanation of the data columns in Sheet1:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name of the originating city block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name of the destination city block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“elec” for electricity, “heat” for heat connections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternative which the given values are for. Specify at least “Base” alternative.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable cost of the flow in the connection. Sometimes given as time series. In that case the correct value is ts:timeseriesname, where a time series CSV file with timeseriesname must be found in the input folder. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">€/kWh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional multiplier for the connection flow cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable cost of the flow in the connection in the reverse direction. Sometimes given as time series. In that case the correct value is ts:timeseriesname, where a time series CSV file with timeseriesname must be found in the input folder. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional multiplier for the connection flow cost in reverse direction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The limit for the flow in the connection. If investments are considered, set this to 1. In that case this is the capacity of one investment unit. If left empty, there is no limit for the connection flow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual amortized investment cost of the connection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€/unit/year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">candidate_units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If given, specifies the maximum number of investment units.</t>
+  </si>
+  <si>
     <t xml:space="preserve">fix_ratio_out_in_connection_flow</t>
   </si>
   <si>
+    <t xml:space="preserve">relationship between the input and output of the connection. Equal to efficiency.</t>
+  </si>
+  <si>
     <t xml:space="preserve">connection_investment_variable_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">elec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ts:price_dayahead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">connection_investment_variable_type_continuous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explanation of the data columns in Sheet1:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name of the originating city block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name of the destination city block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“elec” for electricity, “heat” for heat connections</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alternative which the given values are for. Specify at least “Base” alternative.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable cost of the flow in the connection. Sometimes given as time series. In that case the correct value is ts:timeseriesname, where a time series CSV file with timeseriesname must be found in the input folder. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/kWh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional multiplier for the connection flow cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable cost of the flow in the connection in the reverse direction. Sometimes given as time series. In that case the correct value is ts:timeseriesname, where a time series CSV file with timeseriesname must be found in the input folder. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional multiplier for the connection flow cost in reverse direction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The limit for the flow in the connection. If investments are considered, set this to 1. In that case this is the capacity of one investment unit. If left empty, there is no limit for the connection flow.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annual amortized investment cost of the connection.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/unit/year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">candidate_units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If given, specifies the maximum number of investment units.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">relationship between the input and output of the connection. Equal to efficiency.</t>
   </si>
 </sst>
 </file>
@@ -486,7 +486,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="33.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="26.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="29.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="20.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="41.68"/>
   </cols>
   <sheetData>
@@ -524,25 +524,23 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>1</v>
@@ -553,25 +551,23 @@
       <c r="K2" s="1" t="n">
         <v>0.99</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="L2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>1</v>
@@ -582,14 +578,12 @@
       <c r="K3" s="1" t="n">
         <v>0.99</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="L3" s="3"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L1003" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L1:L1003" type="list">
       <formula1>"connection_investment_variable_type_continuous,connection_investment_variable_type_integer"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -618,18 +612,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -637,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" s="8"/>
       <c r="G4" s="9"/>
@@ -647,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" s="8"/>
       <c r="G5" s="9"/>
@@ -657,7 +651,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" s="8"/>
       <c r="G6" s="9"/>
@@ -667,7 +661,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" s="8"/>
       <c r="G7" s="9"/>
@@ -677,10 +671,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G8" s="9"/>
     </row>
@@ -689,7 +683,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" s="10"/>
       <c r="G9" s="9"/>
@@ -699,7 +693,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="10"/>
       <c r="G10" s="9"/>
@@ -709,7 +703,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="10"/>
       <c r="G11" s="9"/>
@@ -719,10 +713,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -730,33 +724,33 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>

--- a/example_data/connections/connections-input.xlsx
+++ b/example_data/connections/connections-input.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <si>
     <t xml:space="preserve">node1</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t xml:space="preserve">efficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">candidate_connections</t>
   </si>
   <si>
     <t xml:space="preserve">market</t>
@@ -524,23 +527,25 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3"/>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>1</v>
@@ -555,19 +560,19 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>1</v>
@@ -583,7 +588,7 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L1:L1003" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L1003" type="list">
       <formula1>"connection_investment_variable_type_continuous,connection_investment_variable_type_integer"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -612,18 +617,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -631,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="8"/>
       <c r="G4" s="9"/>
@@ -641,7 +646,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="8"/>
       <c r="G5" s="9"/>
@@ -651,7 +656,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="8"/>
       <c r="G6" s="9"/>
@@ -661,7 +666,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="8"/>
       <c r="G7" s="9"/>
@@ -671,10 +676,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8" s="9"/>
     </row>
@@ -683,7 +688,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="10"/>
       <c r="G9" s="9"/>
@@ -693,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="10"/>
       <c r="G10" s="9"/>
@@ -703,7 +708,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="10"/>
       <c r="G11" s="9"/>
@@ -713,10 +718,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -724,33 +729,33 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>

--- a/example_data/connections/connections-input.xlsx
+++ b/example_data/connections/connections-input.xlsx
@@ -556,7 +556,9 @@
       <c r="K2" s="1" t="n">
         <v>0.99</v>
       </c>
-      <c r="L2" s="3"/>
+      <c r="L2" s="3" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
@@ -583,13 +585,15 @@
       <c r="K3" s="1" t="n">
         <v>0.99</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3" t="n">
+        <v>1000</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L1003" type="list">
-      <formula1>"connection_investment_variable_type_continuous,connection_investment_variable_type_integer"</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L1003" type="none">
+      <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/example_data/connections/connections-input.xlsx
+++ b/example_data/connections/connections-input.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
   <si>
     <t xml:space="preserve">node1</t>
   </si>
@@ -477,7 +477,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.45"/>
@@ -587,6 +587,26 @@
       </c>
       <c r="L3" s="3" t="n">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/example_data/connections/connections-input.xlsx
+++ b/example_data/connections/connections-input.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="41">
   <si>
     <t xml:space="preserve">node1</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">highprice</t>
   </si>
   <si>
     <t xml:space="preserve">Explanation of the data columns in Sheet1:</t>
@@ -600,7 +603,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>16</v>
@@ -641,18 +644,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -660,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="8"/>
       <c r="G4" s="9"/>
@@ -670,7 +673,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="8"/>
       <c r="G5" s="9"/>
@@ -680,7 +683,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="8"/>
       <c r="G6" s="9"/>
@@ -690,7 +693,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="8"/>
       <c r="G7" s="9"/>
@@ -700,10 +703,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" s="9"/>
     </row>
@@ -712,7 +715,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="10"/>
       <c r="G9" s="9"/>
@@ -722,7 +725,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="10"/>
       <c r="G10" s="9"/>
@@ -732,7 +735,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="10"/>
       <c r="G11" s="9"/>
@@ -742,10 +745,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -753,33 +756,33 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
